--- a/public/modelo-leads.xlsx
+++ b/public/modelo-leads.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Leads" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,130 +440,1357 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Telefone</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Origem</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Transacao</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Condicao</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Bairro</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Cidade</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Estado</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Quartos</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Suites</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Vagas</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Banheiros</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Area_min</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Area_max</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Valor_min</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Valor_max</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Observacoes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Origem</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Transacao</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Condicao</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bairro</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Quartos</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Suites</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Vagas</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Banheiros</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Area_max</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Valor_max</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Observacoes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>João Silva</v>
-      </c>
-      <c r="B2" t="str">
-        <v>47999999999</v>
-      </c>
-      <c r="C2" t="str">
-        <v>joao@email.com</v>
-      </c>
-      <c r="D2" t="str">
-        <v>portal</v>
-      </c>
-      <c r="E2" t="str">
-        <v>apartamento</v>
-      </c>
-      <c r="F2" t="str">
-        <v>compra</v>
-      </c>
-      <c r="G2" t="str">
-        <v>usado</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Centro</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Itajaí</v>
-      </c>
-      <c r="J2" t="str">
-        <v>SC</v>
-      </c>
-      <c r="K2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PAULA PERSIKE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13996688520</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cidade Ocian</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maria ai que bom vou faser essa receita</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13982142130</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Cidade Ocian</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Márcia Regina Toresan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11997620800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L2">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Katia juli da Silva lopes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11983304623</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>maria elaine estevam</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11983667339</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Boqueirão</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="M2">
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Renata Simone Marcinkowski Andrade de Freitas</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11965771668</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Balneário Maracanã</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Renata Simone Marcinkowski Andrade de Freitas</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11965771668</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jair</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11920077597</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jair</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11920077597</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vila Mirim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Elisângela</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13955411904</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Balneário Maracanã</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Edivaldo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11977029282</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="N2">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13981582019</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Cidade Ocian</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11973609509</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ubiratã Mendes castro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11911543297</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vila Caiçara</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="O2">
-        <v>60</v>
-      </c>
-      <c r="P2">
-        <v>100</v>
-      </c>
-      <c r="Q2">
-        <v>300000</v>
-      </c>
-      <c r="R2">
-        <v>500000</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Prefere andar alto</v>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Wilsonwsn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11962240112</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Luzia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11945882067</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Canto do Forte</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Enedina Mamede</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11972425822</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Valter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11980521562</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Marcos</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15997060614</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cidade Ocian</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAULA PERSIKE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13996688520</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Cidade Ocian</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Michelle Alara</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11997192197</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Balneário Maracanã</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Rogério Faria</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11982240694</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Guilhermina</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Antonio Sena Borges</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13991434306</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Canto do Forte</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rosemeire Freitas</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11995171715</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Guilhermina</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DOMINGOS SÁLVIo Alves de Araújo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11997192197</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Balneário Maracanã</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Márcia Regina Toresan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11997620800</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Guilhermina</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13981695195</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Guilhermina</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>47991449272</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Balneário Maracanã</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amanda Duque</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11958290507</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jair</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>11920077597</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cristiano do carmo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11940024759</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>jordite</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11960362422</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vila Caiçara</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>wilson</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>13996205041</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>comprar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>